--- a/Team-Data/2007-08/12-13-2007-08.xlsx
+++ b/Team-Data/2007-08/12-13-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE2" t="n">
         <v>16</v>
@@ -778,7 +845,7 @@
         <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
         <v>14</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>13.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -972,7 +1039,7 @@
         <v>14</v>
       </c>
       <c r="AU3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
         <v>17</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-5.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
         <v>22</v>
@@ -1151,13 +1218,13 @@
         <v>30</v>
       </c>
       <c r="AT4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU4" t="n">
         <v>26</v>
       </c>
       <c r="AV4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-4</v>
       </c>
       <c r="AD5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
         <v>25</v>
@@ -1318,7 +1385,7 @@
         <v>27</v>
       </c>
       <c r="AO5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP5" t="n">
         <v>25</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -1479,13 +1546,13 @@
         <v>17</v>
       </c>
       <c r="AH6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI6" t="n">
         <v>21</v>
       </c>
       <c r="AJ6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK6" t="n">
         <v>24</v>
@@ -1524,10 +1591,10 @@
         <v>19</v>
       </c>
       <c r="AW6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY6" t="n">
         <v>20</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1725,7 @@
         <v>9</v>
       </c>
       <c r="AG7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH7" t="n">
         <v>19</v>
@@ -1709,7 +1776,7 @@
         <v>29</v>
       </c>
       <c r="AX7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY7" t="n">
         <v>5</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1928,7 @@
         <v>12</v>
       </c>
       <c r="AN8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1879,7 +1946,7 @@
         <v>4</v>
       </c>
       <c r="AT8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU8" t="n">
         <v>3</v>
@@ -1903,7 +1970,7 @@
         <v>1</v>
       </c>
       <c r="BB8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
         <v>6</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2095,7 @@
         <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ9" t="n">
         <v>17</v>
@@ -2088,7 +2155,7 @@
         <v>13</v>
       </c>
       <c r="BC9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2265,7 @@
         <v>8</v>
       </c>
       <c r="AE10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF10" t="n">
         <v>10</v>
@@ -2207,7 +2274,7 @@
         <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2447,7 @@
         <v>1</v>
       </c>
       <c r="AE11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF11" t="n">
         <v>14</v>
@@ -2401,7 +2468,7 @@
         <v>19</v>
       </c>
       <c r="AL11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM11" t="n">
         <v>11</v>
@@ -2437,7 +2504,7 @@
         <v>14</v>
       </c>
       <c r="AX11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY11" t="n">
         <v>13</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2629,7 @@
         <v>8</v>
       </c>
       <c r="AE12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF12" t="n">
         <v>14</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-4.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE13" t="n">
         <v>22</v>
@@ -2780,7 +2847,7 @@
         <v>8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR13" t="n">
         <v>24</v>
@@ -2798,7 +2865,7 @@
         <v>20</v>
       </c>
       <c r="AW13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX13" t="n">
         <v>7</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F14" t="n">
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.619</v>
+        <v>0.6</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
@@ -2863,76 +2930,76 @@
         <v>38.4</v>
       </c>
       <c r="J14" t="n">
-        <v>81.59999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="K14" t="n">
-        <v>0.47</v>
+        <v>0.472</v>
       </c>
       <c r="L14" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M14" t="n">
         <v>20</v>
       </c>
       <c r="N14" t="n">
-        <v>0.359</v>
+        <v>0.363</v>
       </c>
       <c r="O14" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="P14" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.769</v>
+        <v>0.771</v>
       </c>
       <c r="R14" t="n">
         <v>10.7</v>
       </c>
       <c r="S14" t="n">
-        <v>33.8</v>
+        <v>33.6</v>
       </c>
       <c r="T14" t="n">
-        <v>44.5</v>
+        <v>44.3</v>
       </c>
       <c r="U14" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="V14" t="n">
-        <v>16.2</v>
+        <v>16.6</v>
       </c>
       <c r="W14" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.9</v>
+        <v>107.2</v>
       </c>
       <c r="AC14" t="n">
         <v>4.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AE14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
       </c>
       <c r="AG14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH14" t="n">
         <v>21</v>
@@ -2941,7 +3008,7 @@
         <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AK14" t="n">
         <v>5</v>
@@ -2962,7 +3029,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AR14" t="n">
         <v>18</v>
@@ -2971,19 +3038,19 @@
         <v>2</v>
       </c>
       <c r="AT14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV14" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AW14" t="n">
         <v>5</v>
       </c>
       <c r="AX14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY14" t="n">
         <v>16</v>
@@ -2992,10 +3059,10 @@
         <v>20</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC14" t="n">
         <v>7</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3120,7 +3187,7 @@
         <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ15" t="n">
         <v>16</v>
@@ -3132,13 +3199,13 @@
         <v>5</v>
       </c>
       <c r="AM15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN15" t="n">
         <v>3</v>
       </c>
       <c r="AO15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP15" t="n">
         <v>12</v>
@@ -3165,13 +3232,13 @@
         <v>30</v>
       </c>
       <c r="AX15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY15" t="n">
         <v>17</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA15" t="n">
         <v>8</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -3209,94 +3276,94 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E16" t="n">
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>0.273</v>
+        <v>0.286</v>
       </c>
       <c r="H16" t="n">
         <v>48</v>
       </c>
       <c r="I16" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="J16" t="n">
-        <v>76.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="K16" t="n">
         <v>0.463</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="M16" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="N16" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
       <c r="O16" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P16" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="R16" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T16" t="n">
-        <v>39.5</v>
+        <v>39.7</v>
       </c>
       <c r="U16" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="V16" t="n">
         <v>15</v>
       </c>
       <c r="W16" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="X16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y16" t="n">
         <v>3.8</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>-4.8</v>
+        <v>-4.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AE16" t="n">
         <v>26</v>
       </c>
       <c r="AF16" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG16" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AH16" t="n">
         <v>21</v>
@@ -3317,7 +3384,7 @@
         <v>26</v>
       </c>
       <c r="AN16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO16" t="n">
         <v>22</v>
@@ -3344,19 +3411,19 @@
         <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AX16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AY16" t="n">
         <v>4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BB16" t="n">
         <v>25</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-4</v>
       </c>
       <c r="AD17" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
@@ -3499,7 +3566,7 @@
         <v>25</v>
       </c>
       <c r="AN17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO17" t="n">
         <v>20</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3912,7 @@
         <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3887,10 +3954,10 @@
         <v>11</v>
       </c>
       <c r="AV19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX19" t="n">
         <v>17</v>
@@ -3902,7 +3969,7 @@
         <v>27</v>
       </c>
       <c r="BA19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB19" t="n">
         <v>30</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4139,7 @@
         <v>6</v>
       </c>
       <c r="AW20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX20" t="n">
         <v>26</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-8.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4254,7 +4321,7 @@
         <v>18</v>
       </c>
       <c r="AW21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4476,7 @@
         <v>2</v>
       </c>
       <c r="AN22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO22" t="n">
         <v>9</v>
@@ -4427,7 +4494,7 @@
         <v>1</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU22" t="n">
         <v>12</v>
@@ -4442,7 +4509,7 @@
         <v>18</v>
       </c>
       <c r="AY22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ22" t="n">
         <v>12</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4640,7 @@
         <v>20</v>
       </c>
       <c r="AH23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI23" t="n">
         <v>20</v>
@@ -4618,13 +4685,13 @@
         <v>22</v>
       </c>
       <c r="AW23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX23" t="n">
         <v>6</v>
       </c>
       <c r="AY23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ23" t="n">
         <v>13</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -4949,7 +5016,7 @@
         <v>10</v>
       </c>
       <c r="AL25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM25" t="n">
         <v>21</v>
@@ -4958,7 +5025,7 @@
         <v>5</v>
       </c>
       <c r="AO25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP25" t="n">
         <v>24</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE26" t="n">
         <v>22</v>
@@ -5140,7 +5207,7 @@
         <v>20</v>
       </c>
       <c r="AO26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -5211,85 +5278,85 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E27" t="n">
         <v>17</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>0.773</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H27" t="n">
         <v>48</v>
       </c>
       <c r="I27" t="n">
-        <v>37.4</v>
+        <v>37.7</v>
       </c>
       <c r="J27" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K27" t="n">
-        <v>0.472</v>
+        <v>0.475</v>
       </c>
       <c r="L27" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>21</v>
+        <v>20.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0.404</v>
+        <v>0.407</v>
       </c>
       <c r="O27" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P27" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="Q27" t="n">
         <v>0.769</v>
       </c>
       <c r="R27" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="S27" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="T27" t="n">
-        <v>40.5</v>
+        <v>40.2</v>
       </c>
       <c r="U27" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="V27" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="W27" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="X27" t="n">
         <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.5</v>
+        <v>100.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AD27" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AE27" t="n">
         <v>2</v>
@@ -5304,7 +5371,7 @@
         <v>21</v>
       </c>
       <c r="AI27" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AJ27" t="n">
         <v>21</v>
@@ -5316,46 +5383,46 @@
         <v>4</v>
       </c>
       <c r="AM27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN27" t="n">
         <v>2</v>
       </c>
       <c r="AO27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP27" t="n">
         <v>26</v>
       </c>
       <c r="AQ27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR27" t="n">
         <v>26</v>
       </c>
       <c r="AS27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AT27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU27" t="n">
         <v>10</v>
       </c>
       <c r="AV27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW27" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AX27" t="n">
         <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA27" t="n">
         <v>25</v>
@@ -5364,7 +5431,7 @@
         <v>12</v>
       </c>
       <c r="BC27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5553,7 @@
         <v>12</v>
       </c>
       <c r="AI28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ28" t="n">
         <v>5</v>
@@ -5531,7 +5598,7 @@
         <v>19</v>
       </c>
       <c r="AX28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY28" t="n">
         <v>18</v>
@@ -5540,7 +5607,7 @@
         <v>22</v>
       </c>
       <c r="BA28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB28" t="n">
         <v>14</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5735,7 @@
         <v>19</v>
       </c>
       <c r="AI29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ29" t="n">
         <v>8</v>
@@ -5698,7 +5765,7 @@
         <v>21</v>
       </c>
       <c r="AS29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT29" t="n">
         <v>23</v>
@@ -5707,7 +5774,7 @@
         <v>8</v>
       </c>
       <c r="AV29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW29" t="n">
         <v>20</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5920,7 @@
         <v>3</v>
       </c>
       <c r="AJ30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK30" t="n">
         <v>2</v>
@@ -5889,7 +5956,7 @@
         <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW30" t="n">
         <v>2</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
@@ -5939,61 +6006,61 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F31" t="n">
         <v>10</v>
       </c>
       <c r="G31" t="n">
-        <v>0.545</v>
+        <v>0.524</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>37.9</v>
+        <v>37.7</v>
       </c>
       <c r="J31" t="n">
-        <v>83.5</v>
+        <v>83.2</v>
       </c>
       <c r="K31" t="n">
         <v>0.453</v>
       </c>
       <c r="L31" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M31" t="n">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.343</v>
+        <v>0.339</v>
       </c>
       <c r="O31" t="n">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="P31" t="n">
-        <v>25.5</v>
+        <v>25.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.788</v>
+        <v>0.79</v>
       </c>
       <c r="R31" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="S31" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="T31" t="n">
-        <v>44.2</v>
+        <v>44</v>
       </c>
       <c r="U31" t="n">
         <v>20.1</v>
       </c>
       <c r="V31" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="W31" t="n">
         <v>7.6</v>
@@ -6005,31 +6072,31 @@
         <v>4.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>102</v>
+        <v>101.9</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AE31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF31" t="n">
         <v>10</v>
       </c>
       <c r="AG31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH31" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AI31" t="n">
         <v>7</v>
@@ -6041,22 +6108,22 @@
         <v>14</v>
       </c>
       <c r="AL31" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AM31" t="n">
         <v>14</v>
       </c>
       <c r="AN31" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP31" t="n">
         <v>15</v>
       </c>
       <c r="AQ31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR31" t="n">
         <v>4</v>
@@ -6077,10 +6144,10 @@
         <v>13</v>
       </c>
       <c r="AX31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ31" t="n">
         <v>4</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-13-2007-08</t>
+          <t>2007-12-13</t>
         </is>
       </c>
     </row>
